--- a/data/trans_dic/IP31C_R_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31C_R_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 18,49</t>
+          <t>12,25; 24,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 21,84</t>
+          <t>7,04; 18,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,79</t>
+          <t>11,44; 19,6</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 12,56</t>
+          <t>9,29; 23,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 20,44</t>
+          <t>5,74; 16,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 14,21</t>
+          <t>8,93; 17,75</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 26,5</t>
+          <t>2,36; 15,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 13,27</t>
+          <t>7,69; 31,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 16,24</t>
+          <t>6,56; 20,08</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,58</t>
+          <t>4,65; 11,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,37</t>
+          <t>7,05; 17,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,46</t>
+          <t>6,6; 12,56</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,29</t>
+          <t>4,34; 14,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,25</t>
+          <t>2,72; 10,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,17</t>
+          <t>4,33; 10,54</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 8,43</t>
+          <t>5,52; 20,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 18,96</t>
+          <t>0,47; 8,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 10,72</t>
+          <t>3,75; 12,36</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,06</t>
+          <t>8,54; 13,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,99</t>
+          <t>7,43; 11,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,78; 9,51</t>
+          <t>8,6; 11,67</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>33250</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6830; 18804</t>
+          <t>14845; 30008</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13731; 29529</t>
+          <t>7066; 18607</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23826; 42138</t>
+          <t>25346; 43422</t>
         </is>
       </c>
     </row>
@@ -1059,17 +1059,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>23355</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3171; 11686</t>
+          <t>8270; 20774</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7586; 18925</t>
+          <t>5458; 15757</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12906; 26378</t>
+          <t>16438; 32666</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11921</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3332; 13098</t>
+          <t>1317; 8546</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1465; 8275</t>
+          <t>3950; 16328</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6351; 18149</t>
+          <t>7031; 21524</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>34181</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6870; 20658</t>
+          <t>9183; 23021</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7317; 19930</t>
+          <t>12447; 30246</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17258; 36224</t>
+          <t>24673; 46961</t>
         </is>
       </c>
     </row>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>18133</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3006; 11889</t>
+          <t>6281; 20821</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3707; 14676</t>
+          <t>3137; 12498</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8439; 22398</t>
+          <t>11274; 27413</t>
         </is>
       </c>
     </row>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>9382</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>372; 5765</t>
+          <t>3634; 13228</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3082; 13088</t>
+          <t>326; 5882</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4632; 14727</t>
+          <t>5089; 16781</t>
         </is>
       </c>
     </row>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>46350</t>
+          <t>72509</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>64318</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110668</t>
+          <t>130223</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34837; 58335</t>
+          <t>57539; 88077</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51017; 80275</t>
+          <t>45249; 71901</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93147; 130659</t>
+          <t>110330; 149693</t>
         </is>
       </c>
     </row>
